--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E7B018-B781-4BB1-9333-BDDED87BD944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84F26CD-A0C8-484B-8611-27885D584469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1030,27 +1030,51 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+    <row r="7" spans="1:14" ht="41.65" x14ac:dyDescent="0.45">
+      <c r="A7" s="8">
+        <v>46224</v>
+      </c>
+      <c r="B7" s="9">
+        <v>420</v>
+      </c>
+      <c r="C7" s="9">
+        <v>45</v>
+      </c>
+      <c r="D7" s="9">
+        <v>120</v>
+      </c>
+      <c r="E7" s="9">
+        <v>90</v>
+      </c>
+      <c r="F7" s="9">
+        <v>180</v>
+      </c>
+      <c r="G7" s="9">
+        <v>3</v>
+      </c>
+      <c r="H7" s="9">
+        <v>30</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>555</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84F26CD-A0C8-484B-8611-27885D584469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02F1BE1-05FF-4EF1-A006-1F5CC4EC5E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,6 +206,15 @@
   </si>
   <si>
     <t>AUG</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1076,27 +1085,51 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+    <row r="8" spans="1:14" ht="41.65" x14ac:dyDescent="0.45">
+      <c r="A8" s="8">
+        <v>46225</v>
+      </c>
+      <c r="B8" s="9">
+        <v>420</v>
+      </c>
+      <c r="C8" s="9">
+        <v>45</v>
+      </c>
+      <c r="D8" s="9">
+        <v>120</v>
+      </c>
+      <c r="E8" s="9">
+        <v>90</v>
+      </c>
+      <c r="F8" s="9">
+        <v>180</v>
+      </c>
+      <c r="G8" s="9">
+        <v>3</v>
+      </c>
+      <c r="H8" s="9">
+        <v>30</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>555</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02F1BE1-05FF-4EF1-A006-1F5CC4EC5E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6771848-6A19-446A-A093-EF18E6C9E43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,15 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Felt tired in night</t>
   </si>
 </sst>
 </file>
@@ -1132,26 +1141,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B9" s="14">
+        <v>450</v>
+      </c>
+      <c r="C9" s="14">
+        <v>50</v>
+      </c>
+      <c r="D9" s="14">
+        <v>150</v>
+      </c>
+      <c r="E9" s="14">
+        <v>100</v>
+      </c>
+      <c r="F9" s="14">
+        <v>180</v>
+      </c>
+      <c r="G9" s="14">
+        <v>6</v>
+      </c>
+      <c r="H9" s="14">
+        <v>10</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6771848-6A19-446A-A093-EF18E6C9E43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0E99C8-1BBE-443F-8014-F9E6E180C0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1187,26 +1187,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B10" s="14">
+        <v>455</v>
+      </c>
+      <c r="C10" s="14">
+        <v>55</v>
+      </c>
+      <c r="D10" s="14">
+        <v>140</v>
+      </c>
+      <c r="E10" s="14">
+        <v>90</v>
+      </c>
+      <c r="F10" s="14">
+        <v>170</v>
+      </c>
+      <c r="G10" s="14">
+        <v>3</v>
+      </c>
+      <c r="H10" s="14">
+        <v>50</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" s="13"/>
